--- a/tables/xls/it/91_Servizi.xlsx
+++ b/tables/xls/it/91_Servizi.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
   <si>
     <t>NOME</t>
   </si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t>Testo Lungo</t>
+  </si>
+  <si>
+    <t>Numero Decimale</t>
   </si>
   <si>
     <t>[segreteriacampo_it_city]</t>
@@ -195,7 +198,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
     <font>
@@ -525,7 +528,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
@@ -596,20 +599,11 @@
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
@@ -774,10 +768,10 @@
         <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H4" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I4" t="s">
         <v>38</v>
@@ -789,10 +783,10 @@
         <v>38</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N4" t="s">
         <v>47</v>
@@ -805,22 +799,9 @@
       <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
       <c r="E5" t="s">
         <v>45</v>
       </c>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
-      <c r="L5"/>
-      <c r="M5"/>
-      <c r="N5"/>
-      <c r="O5"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
@@ -920,20 +901,6 @@
       <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
-      <c r="N8"/>
-      <c r="O8"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
@@ -1033,7 +1000,6 @@
       <c r="A11" t="s">
         <v>23</v>
       </c>
-      <c r="B11"/>
       <c r="C11" t="s">
         <v>40</v>
       </c>
@@ -1043,20 +1009,12 @@
       <c r="E11" t="s">
         <v>40</v>
       </c>
-      <c r="F11"/>
       <c r="G11" t="s">
         <v>40</v>
       </c>
       <c r="H11" t="s">
         <v>40</v>
       </c>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
@@ -1109,80 +1067,45 @@
       <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-      <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
-      <c r="N13"/>
-      <c r="O13"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
       <c r="G14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J14" t="s">
-        <v>48</v>
-      </c>
-      <c r="K14"/>
-      <c r="L14"/>
-      <c r="M14"/>
-      <c r="N14"/>
-      <c r="O14"/>
+        <v>49</v>
+      </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>27</v>
       </c>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
       <c r="G15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J15" t="s">
-        <v>53</v>
-      </c>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>28</v>
       </c>
-      <c r="B16"/>
       <c r="C16" t="s">
         <v>42</v>
       </c>
@@ -1192,27 +1115,19 @@
       <c r="E16" t="s">
         <v>46</v>
       </c>
-      <c r="F16"/>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H16" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16"/>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16"/>
+        <v>51</v>
+      </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -1220,7 +1135,7 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -1228,7 +1143,7 @@
         <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -1244,7 +1159,7 @@
         <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -1276,21 +1191,12 @@
         <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
--- a/tables/xls/it/91_Servizi.xlsx
+++ b/tables/xls/it/91_Servizi.xlsx
@@ -16,11 +16,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
   <si>
     <t>NOME</t>
   </si>
   <si>
+    <t>INTERVENTO</t>
+  </si>
+  <si>
     <t>ORDINE</t>
   </si>
   <si>
@@ -141,6 +144,12 @@
     <t>No</t>
   </si>
   <si>
+    <t>Testo - Elenco di valori</t>
+  </si>
+  <si>
+    <t>,SI,NO</t>
+  </si>
+  <si>
     <t>Numero Intero</t>
   </si>
   <si>
@@ -150,9 +159,6 @@
     <t>Verrà utilizzata per identificare il servizio sulla mappa</t>
   </si>
   <si>
-    <t>Testo - Elenco di valori</t>
-  </si>
-  <si>
     <t>rosso,nero,blu,verde,grigio,arancione,viola,bianco,giallo</t>
   </si>
   <si>
@@ -187,6 +193,9 @@
   </si>
   <si>
     <t>SERVIZI</t>
+  </si>
+  <si>
+    <t>Servizi</t>
   </si>
   <si>
     <t>Crescente</t>
@@ -532,26 +541,27 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="5.856" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -593,6 +603,9 @@
       </c>
       <c r="N1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -607,10 +620,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -653,10 +666,13 @@
       <c r="O1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -689,21 +705,24 @@
         <v>10</v>
       </c>
       <c r="L2">
+        <v>11</v>
+      </c>
+      <c r="M2">
         <v>13</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>14</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>15</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -747,65 +766,74 @@
       <c r="O3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O4" t="s">
+        <v>49</v>
+      </c>
+      <c r="P4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
         <v>47</v>
       </c>
-      <c r="G4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M4" t="s">
-        <v>55</v>
-      </c>
-      <c r="N4" t="s">
-        <v>47</v>
-      </c>
-      <c r="O4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>255</v>
@@ -814,11 +842,11 @@
         <v>255</v>
       </c>
       <c r="D6">
+        <v>255</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="E6">
-        <v>255</v>
-      </c>
       <c r="F6">
         <v>255</v>
       </c>
@@ -849,349 +877,364 @@
       <c r="O6">
         <v>255</v>
       </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
         <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>41</v>
+      </c>
+      <c r="P7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>41</v>
+      </c>
+      <c r="P9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>40</v>
+      </c>
+      <c r="P10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>41</v>
       </c>
       <c r="H11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>41</v>
+      </c>
+      <c r="I11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>41</v>
+      </c>
+      <c r="P12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>51</v>
+      </c>
+      <c r="K14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="H15" t="s">
         <v>52</v>
       </c>
       <c r="I15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>55</v>
+      </c>
+      <c r="K15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
         <v>46</v>
       </c>
-      <c r="G16" t="s">
-        <v>51</v>
+      <c r="F16" t="s">
+        <v>48</v>
       </c>
       <c r="H16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>53</v>
+      </c>
+      <c r="I16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
-      <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
